--- a/outputs/tables/tab-13-licenciatura.xlsx
+++ b/outputs/tables/tab-13-licenciatura.xlsx
@@ -378,36 +378,36 @@
         </is>
       </c>
       <c r="B2">
-        <v>13946</v>
+        <v>12592</v>
       </c>
       <c r="C2">
-        <v>0.157321095654668</v>
+        <v>0.1718551461245235</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Somente bacharelado</t>
+          <t>Sem vínculo registrado</t>
         </is>
       </c>
       <c r="B3">
-        <v>82791</v>
+        <v>8956</v>
       </c>
       <c r="C3">
-        <v>0.1302919399451631</v>
+        <v>0.1583296114336757</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sem vínculo registrado</t>
+          <t>Somente bacharelado</t>
         </is>
       </c>
       <c r="B4">
-        <v>46771</v>
+        <v>76156</v>
       </c>
       <c r="C4">
-        <v>0.1124200893716192</v>
+        <v>0.1374678291927097</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>9221</v>
+        <v>8099</v>
       </c>
       <c r="C5">
-        <v>0.07016592560459819</v>
+        <v>0.07494752438572663</v>
       </c>
     </row>
   </sheetData>
